--- a/R Markdown/resultados/regionalizacao_acoes_2023.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2023.xlsx
@@ -396,7 +396,7 @@
         <v>2023</v>
       </c>
       <c r="C2">
-        <v>12941532009.74</v>
+        <v>12941532009.7</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -418,7 +418,7 @@
         <v>2023</v>
       </c>
       <c r="C3">
-        <v>7362960501.23</v>
+        <v>7362960500.940001</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -440,7 +440,7 @@
         <v>2023</v>
       </c>
       <c r="C4">
-        <v>6367485616.74</v>
+        <v>6367485616.66</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -462,7 +462,7 @@
         <v>2023</v>
       </c>
       <c r="C5">
-        <v>5300000000.21</v>
+        <v>5300000000</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -506,13 +506,13 @@
         <v>2023</v>
       </c>
       <c r="C7">
-        <v>5051432880.75</v>
+        <v>5051432880.67</v>
       </c>
       <c r="D7">
         <v>1091781917.21</v>
       </c>
       <c r="E7">
-        <v>0.2161331137092928</v>
+        <v>0.2161331137127157</v>
       </c>
       <c r="F7">
         <v>32</v>
@@ -682,10 +682,10 @@
         <v>2023</v>
       </c>
       <c r="C15">
-        <v>1248287707.69</v>
+        <v>1248287707.71</v>
       </c>
       <c r="D15">
-        <v>1248287707.69</v>
+        <v>1248287707.71</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>2023</v>
       </c>
       <c r="C25">
-        <v>650361078.84</v>
+        <v>650361078.85</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1467,7 +1467,8 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D_</t>
+          <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
+</t>
         </is>
       </c>
       <c r="B51">
@@ -1584,7 +1585,7 @@
         <v>2023</v>
       </c>
       <c r="C56">
-        <v>185710716.51</v>
+        <v>185710716.49</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -7209,7 +7210,8 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Operação e Manutenção do Portal da PMSP_x000D_</t>
+          <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
+</t>
         </is>
       </c>
       <c r="B312">
